--- a/output/pdf_financials_xlsx/SECU.xlsx
+++ b/output/pdf_financials_xlsx/SECU.xlsx
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.488273</v>
+        <v>-0.488273</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.486174</v>
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.488273</v>
+        <v>-0.488273</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.369606</v>
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.488273</v>
+        <v>-0.488273</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.369606</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.488273</v>
+        <v>-0.488273</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.486174</v>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.488273</v>
+        <v>-0.488273</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.486074</v>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-23.97660097002308</v>
@@ -74166,7 +74166,7 @@
         </is>
       </c>
       <c r="E841" s="5" t="n">
-        <v>0.488273</v>
+        <v>-0.488273</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SECU.xlsx
+++ b/output/pdf_financials_xlsx/SECU.xlsx
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.058094</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.280404</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -996,16 +996,16 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.847398</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.8286829999999999</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.7234429999999999</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.399037</v>
       </c>
     </row>
     <row r="13">
@@ -1814,10 +1814,10 @@
         <v>-0.488273</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.486174</v>
+        <v>-0.42808</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.887353</v>
+        <v>-4.606949</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1846,16 +1846,16 @@
         <v>2.589782</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.314057</v>
+        <v>-2.161455</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.144349</v>
+        <v>-0.684334</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1.103336</v>
+        <v>0.379893</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.324989</v>
+        <v>-0.074048</v>
       </c>
     </row>
     <row r="28">
@@ -1920,10 +1920,10 @@
         <v>-0.488273</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.486074</v>
+        <v>-0.42798</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.883313</v>
+        <v>-4.602909</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>2.589782</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.314057</v>
+        <v>-2.161455</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.669274</v>
+        <v>0.840591</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>2.634482</v>
+        <v>1.911039</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.855272</v>
+        <v>1.456235</v>
       </c>
     </row>
     <row r="30">
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-96.22439517297015</v>
+        <v>-90.69910828186127</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -2010,16 +2010,16 @@
         <v>12.77285093859011</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-2.644161947692938</v>
+        <v>-4.349306812908907</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>1.5306688582418</v>
+        <v>0.7707940495199308</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>2.184064859401512</v>
+        <v>1.584308841300037</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>1.553619224966864</v>
+        <v>1.219462532755101</v>
       </c>
     </row>
     <row r="31">
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.327015</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>1.51047</v>
@@ -2157,25 +2157,25 @@
         <v>30.442985</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>24.7722</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>17.614846</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>14.87677</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>11.43946</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>27.234152</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>28.79576</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>11.195115</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>14.843347</v>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.327015</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>14.316375</v>
@@ -2249,25 +2249,25 @@
         <v>30.442985</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>24.7722</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>17.614846</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>14.87677</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>11.43946</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>27.234152</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>28.79576</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>11.195115</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>14.843347</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.327015</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.9900139999999999</v>
@@ -2801,25 +2801,25 @@
         <v>7.568791</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>64.331526</v>
+        <v>39.559326</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>35.819487</v>
+        <v>18.204641</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>27.557423</v>
+        <v>12.680653</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>20.891977</v>
+        <v>9.452517</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>34.626756</v>
+        <v>7.392604</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>34.23515</v>
+        <v>5.43939</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>13.774125</v>
+        <v>2.57901</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>1.496118</v>
@@ -6357,19 +6357,19 @@
         <v>0</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.153455</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.222464</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.830635</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-1.072335</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.895743</v>
       </c>
     </row>
     <row r="125">
@@ -6403,19 +6403,19 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.153455</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.222464</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.830635</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-1.072335</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.895743</v>
       </c>
     </row>
     <row r="126">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -19758,7 +19758,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -25262,7 +25262,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -27469,7 +27469,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E256" s="5" t="n">
@@ -30181,7 +30181,11 @@
           <t>Principal lease payments 9</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -32186,7 +32190,11 @@
           <t>Principal lease payments 11</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -34060,7 +34068,11 @@
           <t>Principal lease payments 12</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -49436,7 +49448,7 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
@@ -49515,7 +49527,7 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -69940,7 +69952,7 @@
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
@@ -72779,7 +72791,7 @@
       </c>
       <c r="D824" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E824" t="inlineStr">

--- a/output/pdf_financials_xlsx/SECU.xlsx
+++ b/output/pdf_financials_xlsx/SECU.xlsx
@@ -1901,13 +1901,13 @@
         <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>1.524925</v>
+        <v>3.483977</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1.531146</v>
+        <v>3.845726</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.530283</v>
+        <v>3.907247</v>
       </c>
     </row>
     <row r="29">
@@ -1955,13 +1955,13 @@
         <v>-2.161455</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.840591</v>
+        <v>2.799643</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.911039</v>
+        <v>4.225619</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.456235</v>
+        <v>3.833199</v>
       </c>
     </row>
     <row r="30">
@@ -2013,13 +2013,13 @@
         <v>-4.349306812908907</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.7707940495199308</v>
+        <v>2.567179716628095</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1.584308841300037</v>
+        <v>3.503165315655737</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>1.219462532755101</v>
+        <v>3.209950702389601</v>
       </c>
     </row>
     <row r="31">
@@ -5206,10 +5206,10 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.00404</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0</v>
@@ -5233,13 +5233,13 @@
         <v>0</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>3.483977</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>3.845726</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>3.907247</v>
       </c>
     </row>
     <row r="101">
@@ -28374,7 +28374,11 @@
           <t>Depreciation of property and equipment 6</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -28455,7 +28459,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -30827,7 +30831,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -30908,7 +30916,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -46368,7 +46376,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -49205,7 +49213,11 @@
           <t>Depreciation of property and equipment 6</t>
         </is>
       </c>
-      <c r="D528" t="inlineStr"/>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E528" t="inlineStr">
         <is>
           <t>-</t>
@@ -49286,7 +49298,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -56617,7 +56629,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D622" t="inlineStr"/>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E622" t="inlineStr">
         <is>
           <t>-</t>
@@ -56698,7 +56714,7 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
@@ -72548,7 +72564,7 @@
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E821" t="inlineStr">

--- a/output/pdf_financials_xlsx/SECU.xlsx
+++ b/output/pdf_financials_xlsx/SECU.xlsx
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.019094</v>
       </c>
       <c r="C67" s="3" t="n">
         <v>0</v>
@@ -5896,10 +5896,10 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>2.694095</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>12.805905</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.005985</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.017155</v>
       </c>
       <c r="E116" s="3" t="n">
         <v>0</v>
@@ -5963,13 +5963,13 @@
         <v>0</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-1.366442</v>
       </c>
       <c r="K116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.029113</v>
       </c>
       <c r="M116" s="3" t="n">
         <v>0</v>
@@ -6131,15 +6131,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M119" s="3" t="n">
+        <v>1.459612</v>
+      </c>
+      <c r="N119" s="3" t="n">
+        <v>-0.914353</v>
       </c>
     </row>
     <row r="120">
@@ -6210,28 +6206,28 @@
         <v>0</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-2.023558</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0</v>
+        <v>-15.904966</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-7.235684</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-1.398535</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-2.177059</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-0.94786</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-1.649482</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-1.115566</v>
       </c>
     </row>
     <row r="122">
@@ -6889,65 +6885,45 @@
       <c r="B135" s="3" t="n">
         <v>-0.350618</v>
       </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C135" s="3" t="n">
+        <v>0.955369</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>3.182384</v>
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F135" s="3" t="n">
+        <v>22.50091</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>25.272218</v>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>22.7205</v>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>16.366701</v>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>0.897833</v>
       </c>
       <c r="K135" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L135" s="3" t="n">
+        <v>1.374124</v>
+      </c>
+      <c r="M135" s="3" t="n">
+        <v>0.879203</v>
+      </c>
+      <c r="N135" s="3" t="n">
+        <v>1.616447</v>
       </c>
     </row>
   </sheetData>
@@ -29733,7 +29709,11 @@
           <t>Cash generated from operating activities $</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -30268,7 +30248,11 @@
           <t>Purchase of common shares 11</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -30347,7 +30331,11 @@
           <t>Proceeds from shares issued 11</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -32042,7 +32030,11 @@
           <t>Purchase of intangible assets 9</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -32281,7 +32273,11 @@
           <t>Purchase of common shares 13</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -32356,7 +32352,11 @@
           <t>Proceeds from shares issued 13</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -32581,7 +32581,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -33693,7 +33697,11 @@
           <t>Purchase of intangible assets 10</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -35660,7 +35668,11 @@
           <t>Purchase of common shares 14</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E359" t="inlineStr">
         <is>
           <t>-</t>
@@ -35739,7 +35751,11 @@
           <t>Proceeds from shares issued 14</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E360" t="inlineStr">
         <is>
           <t>-</t>
@@ -37007,7 +37023,11 @@
           <t>Cash generated from operating activities $</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
           <t>-</t>
@@ -37706,7 +37726,11 @@
           <t>Purchase of common shares 15</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>
@@ -37785,7 +37809,11 @@
           <t>Proceeds from shares issued</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr">
         <is>
           <t>-</t>
@@ -39764,7 +39792,11 @@
           <t>Purchase of common shares</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -40080,7 +40112,11 @@
           <t>Deferred income tax recovery 18</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
           <t>-</t>
@@ -43849,7 +43885,11 @@
           <t>Proceeds from shares issued 13 1,094,000</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
@@ -45878,7 +45918,11 @@
           <t>Proceeds from shares issued 8 64,000</t>
         </is>
       </c>
-      <c r="D487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E487" t="inlineStr">
         <is>
           <t>-</t>
@@ -47342,7 +47386,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
           <t>-</t>
@@ -47502,7 +47550,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E507" t="inlineStr">
         <is>
           <t>-</t>
@@ -73366,7 +73418,11 @@
           <t>Income tax recovery 13</t>
         </is>
       </c>
-      <c r="D831" t="inlineStr"/>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E831" t="inlineStr">
         <is>
           <t>-</t>
